--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -214,6 +214,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -600,7 +603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13</t>
+          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 18:55</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1147,52 +1150,52 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="13">
-      <c r="A2" s="5" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
+      <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K2" t="n">
+        <v>771</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="13">
@@ -1201,46 +1204,95 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>26750</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1255,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="110" customWidth="1" style="13" min="1" max="1"/>
@@ -1275,31 +1327,59 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="22.05" customHeight="1" s="13">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
+语义模型
+- 兼容级别 1606 → 1702，启用 DAX 原生 function（UDF）
+- 新增 functions.tmdl：FormatKFM（按单位动态格式）、FormatKFM2（日报比率格式）、PriorYearMonthValue（去年同期年累计）
+- 新增事实表 L1-KFM日报（27 列，SAP BW ZRPP_CP006 数据源）
+- 新增映射表 日报指标映射、月报指标映射（各 6 列），取代原「指标映射」表
+- KFM选冶厂月报 新增「全年预算数」列（18→19 列）
+- 度量值 15→23：新增日报度量（日完成、月累计、月计划L1、月比计划L1、年计划L1、年累计完成L1、年比计划L1、标题-日报），「标题」改名「标题-月报」，度量值改用 formatStringDefinition 引用 UDF
+- 新增 Power Query 参数 p_日报起始日期（2026-01-01），表达式 全年预算表、月累计预测表
+报告层
+- 新增「KFM日报」页面（5 个视觉对象），设为落地页
+- 页面 3→4，视觉对象 30→35
+- 更新 zh-CN 文化翻译
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="13"/>
+    <row r="6" ht="6" customHeight="1" s="13">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" s="13">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="7" ht="22.05" customHeight="1" s="13">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="6" customHeight="1" s="13"/>
-    <row r="7" ht="22.05" customHeight="1" s="13">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8" ht="409.6" customHeight="1" s="13"/>
+    <row r="9" ht="6" customHeight="1" s="13">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="409.6" customHeight="1" s="13">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -1331,7 +1411,6 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" s="13"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,13 +1618,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9FAB0E3-5A55-4C0B-B899-52611175B27E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C6DC86F-49DE-4A15-95DA-33EDB47744A0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0845D185-CF8F-477B-8044-36F08765261D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B761054-97E1-4631-B0D0-26187888F742}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE5686C2-C761-478B-89FF-6E5E92BDF743}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCDFAEB4-0B9F-4EFC-B059-0E2CD76B4AE4}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -1055,7 +1055,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01；表达式：全年预算表、月累计预测表</t>
+          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01（中间表 全年预算表、月累计预测表 已内联进 L1-KFM日报）</t>
         </is>
       </c>
     </row>
@@ -1414,217 +1414,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x0101005D1433F41EF0D1478250392B90115F38" ma:contentTypeVersion="9" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="032b99cbe0032f0cff5a48f1014b19a5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6652493-9e78-432e-96e9-9f560552d737" xmlns:ns3="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="587c6ea9c9f887b9a4e3544120a7e33e" ns2:_="" ns3:_="">
-    <xsd:import namespace="c6652493-9e78-432e-96e9-9f560552d737"/>
-    <xsd:import namespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c6652493-9e78-432e-96e9-9f560552d737" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="图像标记" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b2d6801b-f0bd-476f-bc0d-7adc71382b76" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8260f861-705f-495b-b301-6e45a48115a7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6652493-9e78-432e-96e9-9f560552d737">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C6DC86F-49DE-4A15-95DA-33EDB47744A0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B761054-97E1-4631-B0D0-26187888F742}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCDFAEB4-0B9F-4EFC-B059-0E2CD76B4AE4}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -603,7 +603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 18:55</t>
+          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 19:15</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1155,96 +1155,96 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="13">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>48112a2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-10-13 18:55:27</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>35</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>5662</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>771</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="13">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1253,46 +1253,95 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>26750</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1307,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="110" customWidth="1" style="13" min="1" max="1"/>
@@ -1330,12 +1379,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" s="13">
       <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表
+- 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
+- 删除 expressions.tmdl 中的这两个中间表 expression
+- 更新 model.tmdl 的 PBI_QueryOrder 查询顺序注解
+- 同步更新项目概述
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="13">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="6" customHeight="1" s="13">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -1354,32 +1422,32 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" s="13"/>
-    <row r="6" ht="6" customHeight="1" s="13">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="22.05" customHeight="1" s="13"/>
+    <row r="8" ht="409.6" customHeight="1" s="13">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.05" customHeight="1" s="13">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="9" ht="6" customHeight="1" s="13">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="409.6" customHeight="1" s="13"/>
-    <row r="9" ht="6" customHeight="1" s="13">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述

--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -55,12 +55,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="FF1F4E79"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
       <family val="3"/>
@@ -68,14 +62,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="宋体"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -92,13 +89,8 @@
         <fgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF1F8"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,55 +113,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -192,28 +140,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -583,18 +511,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="30" customWidth="1" style="13" min="1" max="1"/>
-    <col width="14" customWidth="1" style="13" min="2" max="2"/>
-    <col width="20" customWidth="1" style="13" min="3" max="3"/>
-    <col width="12" customWidth="1" style="13" min="4" max="4"/>
-    <col width="18" customWidth="1" style="13" min="5" max="5"/>
-    <col width="10" customWidth="1" style="13" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="17.65" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>KFM选冶厂月报 项目概述</t>
         </is>
@@ -603,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 19:15</t>
+          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 19:31</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>一、报告层（KFM选冶厂月报.Report）</t>
         </is>
@@ -622,12 +550,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>页面名称</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -689,7 +617,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>二、语义模型（KFM选冶厂月报.SemanticModel）</t>
         </is>
@@ -703,7 +631,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>事实表 KFM选冶厂月报（19 列）</t>
         </is>
@@ -819,7 +747,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>事实表 L1-KFM日报（27 列）</t>
         </is>
@@ -979,7 +907,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>映射表（各 6 列）：日报指标映射、月报指标映射</t>
         </is>
@@ -1018,7 +946,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>度量值表（23 个度量值）</t>
         </is>
@@ -1046,7 +974,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>DAX 函数（functions.tmdl，3 个）：FormatKFM（按单位动态格式）、FormatKFM2（日报比率格式）、PriorYearMonthValue（去年同期年累计）</t>
         </is>
@@ -1077,95 +1005,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="6" customWidth="1" style="13" min="1" max="1"/>
-    <col width="10" customWidth="1" style="13" min="2" max="2"/>
-    <col width="42" customWidth="1" style="13" min="3" max="3"/>
-    <col width="20" customWidth="1" style="13" min="4" max="4"/>
-    <col width="12" customWidth="1" style="13" min="5" max="5"/>
-    <col width="26" customWidth="1" style="13" min="6" max="6"/>
-    <col width="46" customWidth="1" style="13" min="7" max="7"/>
-    <col width="8" customWidth="1" style="13" min="8" max="8"/>
-    <col width="12" customWidth="1" style="13" min="9" max="9"/>
-    <col width="10" customWidth="1" style="13" min="10" max="11"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.05" customHeight="1" s="13">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>短哈希</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>完整哈希</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>提交日期</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>作者</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>作者邮箱</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>提交信息</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>分支</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>变更文件数</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>新增行</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>删除行</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="13">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>6b4084c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-13 19:31:50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1178,9 +1106,9 @@
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1189,159 +1117,208 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>48112a2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-10-13 18:55:27</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>35</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>5662</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>771</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>26750</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1356,21 +1333,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="110" customWidth="1" style="13" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" s="13">
-      <c r="A1" s="17" t="inlineStr">
+    <row r="1" ht="22.9" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Git 提交备注信息</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="13">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="13.9" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>以下为每个 git 提交的完整提交说明（含标题与正文），直接读取自本地仓库。</t>
         </is>
@@ -1379,12 +1356,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="108" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
+- Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
+- 去掉未使用的维度字段：产品、环节名、产线代码
+- 合并「标准日期」类型转换，删除末尾「已更改列类型」步骤
+- 步骤命名统一为语义化中文名，精简注释
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.05" customHeight="1" s="13">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="6" ht="256.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -1395,15 +1391,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" s="13">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="6" customHeight="1" s="13">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="8" ht="16.9" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -1422,32 +1418,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22.05" customHeight="1" s="13"/>
-    <row r="8" ht="409.6" customHeight="1" s="13">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="45" customHeight="1"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" s="13">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="11" ht="16.9" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12" ht="409.5" customHeight="1"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述

--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 19:31</t>
+          <t>KFM选冶厂月度生产指标完成情况月报，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-13 19:45</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6b4084c</t>
+          <t>1485d55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-13 19:31:50</t>
+          <t>2026-10-13 19:45:55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K2" t="n">
-        <v>143</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>6b4084c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-13 19:31:50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -1181,96 +1181,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>48112a2</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-10-13 18:55:27</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>35</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>5662</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>771</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1279,46 +1279,95 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>26750</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1333,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1356,12 +1405,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="108" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并
+- KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
+- 度量值、日报指标映射、月报指标映射：步骤名改为语义化中文
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="256.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -1372,15 +1438,15 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="256.5" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="8" ht="16.9" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -1391,15 +1457,15 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.9" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -1418,32 +1484,32 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11" ht="16.9" customHeight="1"/>
+    <row r="12" ht="409.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.9" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="409.5" customHeight="1"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述

--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -1927,4 +1927,217 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x0101005D1433F41EF0D1478250392B90115F38" ma:contentTypeVersion="9" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="032b99cbe0032f0cff5a48f1014b19a5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c6652493-9e78-432e-96e9-9f560552d737" xmlns:ns3="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="587c6ea9c9f887b9a4e3544120a7e33e" ns2:_="" ns3:_="">
+    <xsd:import namespace="c6652493-9e78-432e-96e9-9f560552d737"/>
+    <xsd:import namespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c6652493-9e78-432e-96e9-9f560552d737" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="图像标记" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b2d6801b-f0bd-476f-bc0d-7adc71382b76" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8260f861-705f-495b-b301-6e45a48115a7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6652493-9e78-432e-96e9-9f560552d737">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="81bdbfe7-c43e-4d85-9d9d-9a2adcba7e19" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6166F887-B03F-4D3C-8DFE-3DDF6D0F23BB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FAC3F2B-9200-4CB3-B2AC-8E258D9B59ED}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CF1F3F6-CFA4-4DF3-8560-B67F2332D842}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -1192,7 +1192,7 @@
     <row r="37" ht="22.05" customHeight="1" s="13">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>DAX 函数（functions.tmdl，3 个）：FormatKFM（按单位动态格式）、FormatKFM2（日报比率格式）、PriorYearMonthValue（去年同期年累计）</t>
+          <t>DAX 函数（functions.tmdl，3 个）：FormatAmount（数量格式）、FormatRatio（比率格式）、SameMonthPriorYear（去年同月）</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>9f32794</t>
+          <t>07f180b</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 06:22:46</t>
+          <t>2026-10-14 07:21:58</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="I2" s="12" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>695</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12" t="n">
-        <v>697</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="13">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>07301c6</t>
+          <t>2d4f16f</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:57:45</t>
+          <t>2026-10-14 07:01:02</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+          <t>新增 KFM日月报语义模型分析报告</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>2</v>
+        <v>320</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="13">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>1485d55</t>
+          <t>5ba71b7</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:45:55</t>
+          <t>2026-10-14 06:57:45</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="I4" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>227</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="13">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>6b4084c</t>
+          <t>cea3882</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:31:50</t>
+          <t>2026-10-14 06:34:36</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+          <t>优化语义模型自定义函数命名</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="I5" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>143</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="13">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>9f32794</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-14 06:22:46</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="I6" s="12" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>21</v>
+        <v>695</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>28</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="13">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>48112a2</t>
+          <t>07301c6</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 18:55:27</t>
+          <t>2026-10-13 19:57:45</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1617,32 +1617,32 @@
         </is>
       </c>
       <c r="I7" s="15" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>5662</v>
+        <v>2</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="13">
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>69bb2ba</t>
+          <t>1485d55</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 01:42:09</t>
+          <t>2026-10-13 19:45:55</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1666,61 +1666,257 @@
         </is>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="13">
       <c r="A9" s="15" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="13">
+      <c r="A10" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="13">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="13">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I13" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J13" s="15" t="n">
         <v>26750</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="K13" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1735,7 +1931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="13" min="1" max="1"/>
@@ -1758,12 +1954,81 @@
     <row r="3" ht="20" customHeight="1" s="13">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="118.5" customHeight="1" s="13">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段
+- 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
+- 年累计完成L1：VAR A 字段由「累计预测数」改为「当月累计实际数」
+- 年比计划L1：补充 displayFolder 归入「日报」
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="87.5" customHeight="1" s="13">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告
+HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="103" customHeight="1" s="13">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑
+- functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
+- 度量值.tmdl：补充 月比计划L1/年比计划L1/年累计完成L1 的逻辑注释，修正 标题-日报 开头错位的遗留注释
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="13">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="118.5" customHeight="1" s="13">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名
+- FormatKFM → FormatAmount（数量格式）
+- FormatKFM2 → FormatRatio（比率格式）
+- PriorYearMonthValue → SameMonthPriorYear（去年同月）
+Co-Authored-By: Claude Opus 4.8 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="105.5" customHeight="1" s="13">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="12" ht="87.5" customHeight="1" s="13">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -1771,15 +2036,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="13">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="120" customHeight="1" s="13">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="14" ht="87.5" customHeight="1" s="13">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -1787,15 +2052,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="13">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="13">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="120" customHeight="1" s="13">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="16" ht="103" customHeight="1" s="13">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -1804,15 +2069,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" s="13">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="13">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="279.5" customHeight="1" s="13">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="18" ht="134" customHeight="1" s="13">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -1823,15 +2088,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="13">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="19" ht="20" customHeight="1" s="13">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="47.55" customHeight="1" s="13">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="20" ht="134" customHeight="1" s="13">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -1842,15 +2107,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="13">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="409.6" customHeight="1" s="13">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="22" ht="273.5" customHeight="1" s="13">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -1869,30 +2134,30 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="23" ht="20" customHeight="1" s="13">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="24" ht="56.5" customHeight="1" s="13">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="13">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="26" ht="506" customHeight="1" s="13">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -1924,6 +2189,26 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2131,13 +2416,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6166F887-B03F-4D3C-8DFE-3DDF6D0F23BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E244B380-A348-4BF1-AE04-572D66D0D3A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FAC3F2B-9200-4CB3-B2AC-8E258D9B59ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CB6ED6E-3706-4FF1-8A86-7BDD94DA1745}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CF1F3F6-CFA4-4DF3-8560-B67F2332D842}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6531DC04-AC6B-4FC9-BC1E-B8CD1DE54F43}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>累计预测数</t>
+          <t>累计实际数</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="38" ht="35" customHeight="1" s="13">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01（中间表 全年预算表、月累计预测表 已内联进 L1-KFM日报）</t>
+          <t>Power Query 参数：p_月报起始日期=2025-01-01、p_日报起始日期=2026-01-01、服务器/系统编号/客户端ID/SharePoint站点（中间表 全年预算表、月累计实际表 已内联进 L1-KFM日报）</t>
         </is>
       </c>
       <c r="B38" s="26" t="n"/>
@@ -1260,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>07f180b</t>
+          <t>630c17f</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 07:21:58</t>
+          <t>2026-10-14 10:06:29</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+          <t>更新语义模型分析报告：同步本轮修复</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -1375,10 +1375,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K2" s="12" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="13">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2d4f16f</t>
+          <t>1794160</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 07:01:02</t>
+          <t>2026-10-14 10:06:24</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
+          <t>调整报告视觉对象布局与筛选</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="I3" s="15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>320</v>
+        <v>37</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="13">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>5ba71b7</t>
+          <t>9cbf408</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 06:57:45</t>
+          <t>2026-10-14 10:06:18</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+          <t>修复语义模型分析报告发现的问题</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="I4" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="13">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>cea3882</t>
+          <t>07f180b</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 06:34:36</t>
+          <t>2026-10-14 07:21:58</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>优化语义模型自定义函数命名</t>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="I5" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="13">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>9f32794</t>
+          <t>2d4f16f</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 06:22:46</t>
+          <t>2026-10-14 07:01:02</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+          <t>新增 KFM日月报语义模型分析报告</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="I6" s="12" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>695</v>
+        <v>320</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="13">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>07301c6</t>
+          <t>5ba71b7</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:57:45</t>
+          <t>2026-10-14 06:57:45</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="I7" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="13">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>1485d55</t>
+          <t>cea3882</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:45:55</t>
+          <t>2026-10-14 06:34:36</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+          <t>优化语义模型自定义函数命名</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="I8" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>227</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="13">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>6b4084c</t>
+          <t>9f32794</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:31:50</t>
+          <t>2026-10-14 06:22:46</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>130</v>
+        <v>695</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>143</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="13">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>07301c6</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-13 19:57:45</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="I10" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="13">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>48112a2</t>
+          <t>1485d55</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 18:55:27</t>
+          <t>2026-10-13 19:45:55</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>5662</v>
+        <v>134</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>771</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="13">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>69bb2ba</t>
+          <t>6b4084c</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 01:42:09</t>
+          <t>2026-10-13 19:31:50</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1865,10 +1865,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="13">
@@ -1877,46 +1877,193 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="13">
+      <c r="A14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="13">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="13">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I16" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J16" s="12" t="n">
         <v>26750</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K16" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1931,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="13" min="1" max="1"/>
@@ -1954,12 +2101,71 @@
     <row r="3" ht="20" customHeight="1" s="13">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="118.5" customHeight="1" s="13">
       <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复
+- 同步年累计完成L1 新口径与新增参数、中间表变化
+- 问题清单移除已修复的 7 项，保留 4 项并新增 SharePoint 读取提示
+- 更新摘要问题计数与优先处理顺序
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118.5" customHeight="1" s="13">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选
+- 按钮/书签视觉对象位置与尺寸微调
+- 更新日期筛选默认值（2026.08.21 → 2026.08.28）
+- 视觉对象显隐与 tabOrder 调整，表格新增按日期降序排序
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="196" customHeight="1" s="13">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题
+- 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
+- 日报「类别2」四个值的前导空格清理
+- 两个内联中间表聚合由 List.Average 改为 List.Max
+- 「最近月份」过滤改为仅排除 null，不再误判 0 值月份
+- 「标准日期」改用 Date.FromText 按 yyyy.MM.dd 显式解析
+- SAP BW 服务器/系统编号/客户端ID 参数化
+- 映射表数据源由本地硬编码路径改为 SharePoint.Files
+- 序号/环节序号 dataType 由 int64 调整为 double
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="13">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="118.5" customHeight="1" s="13">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -1969,15 +2175,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="13">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="87.5" customHeight="1" s="13">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="12" ht="87.5" customHeight="1" s="13">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -1985,15 +2191,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="13">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="103" customHeight="1" s="13">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="14" ht="103" customHeight="1" s="13">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2002,15 +2208,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" s="13">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="13">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="118.5" customHeight="1" s="13">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="16" ht="118.5" customHeight="1" s="13">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2020,15 +2226,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="13">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="13">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="87.5" customHeight="1" s="13">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="18" ht="87.5" customHeight="1" s="13">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2036,15 +2242,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="19" ht="20" customHeight="1" s="13">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="87.5" customHeight="1" s="13">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="20" ht="87.5" customHeight="1" s="13">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2052,15 +2258,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" s="13">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="13">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="103" customHeight="1" s="13">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="22" ht="103" customHeight="1" s="13">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2069,15 +2275,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="13">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="23" ht="20" customHeight="1" s="13">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="134" customHeight="1" s="13">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="24" ht="134" customHeight="1" s="13">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2088,15 +2294,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1" s="13">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="13">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="134" customHeight="1" s="13">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="26" ht="134" customHeight="1" s="13">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2107,15 +2313,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" s="13">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="27" ht="20" customHeight="1" s="13">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="273.5" customHeight="1" s="13">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="28" ht="273.5" customHeight="1" s="13">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2134,30 +2340,30 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" s="13">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="29" ht="20" customHeight="1" s="13">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="56.5" customHeight="1" s="13">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="30" ht="56.5" customHeight="1" s="13">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="13">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1" s="13">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="506" customHeight="1" s="13">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="32" ht="506" customHeight="1" s="13">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2189,12 +2395,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
@@ -2209,6 +2409,12 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2416,13 +2622,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E244B380-A348-4BF1-AE04-572D66D0D3A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{167067B0-C95C-4D8B-B093-5C83C7776AB2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CB6ED6E-3706-4FF1-8A86-7BDD94DA1745}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C90D35-9711-472B-AD53-8939EF8495CC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6531DC04-AC6B-4FC9-BC1E-B8CD1DE54F43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2474163F-545A-44AE-B6FF-35C08FDAD181}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -760,7 +760,7 @@
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>KFM选冶厂月报UI Enhance</t>
+          <t>KFM月报UIE</t>
         </is>
       </c>
       <c r="B7" s="25" t="n"/>
@@ -776,7 +776,7 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>KFM选冶厂月报</t>
+          <t>KFM月报</t>
         </is>
       </c>
       <c r="B8" s="25" t="n"/>
@@ -834,14 +834,14 @@
     <row r="13" ht="20" customHeight="1" s="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>事实表 KFM选冶厂月报（19 列）</t>
+          <t>事实表 KFM选冶厂月报（18 列）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="13">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>产品分类</t>
+          <t>累计实际数</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -851,261 +851,209 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>总类别</t>
+          <t>累计预算数</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="13">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>实际数</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>累计预算数</t>
+          <t>预测数</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>类别2</t>
+          <t>预算数</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" s="13">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>实际数</t>
+          <t>月份</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>指标项</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>序号</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" s="13">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>预测数</t>
+          <t>总类别</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>指标项</t>
+          <t>类别2</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>环节序号</t>
+          <t>日期</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" s="13">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>预算数</t>
+          <t>环节序号</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>月份-筛选器</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>月份-筛选器</t>
+          <t>排序</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" s="13">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>累计实际数</t>
+          <t>产品分类</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>排序</t>
+          <t>全年预算数</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" s="13">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>全年预算数</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="13">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>事实表 L1-KFM日报（27 列）</t>
+          <t>事实表 L1-KFM日报（15 列）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" s="13">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>产线</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>当日实际数</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>指标类型</t>
+          <t>当月累计实际数</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" s="13">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>地域</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>运营形式</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>指标编码</t>
+          <t>类别2</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" s="13">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>指标编码代码</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>指标名称</t>
+          <t>总类别</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>当日实际数</t>
+          <t>环节序号</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" s="13">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>当月累计实际数</t>
+          <t>全年预算数</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>日期（月份）</t>
+          <t>月计划</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>指标名</t>
+          <t>月预算</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" s="13">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>地域</t>
+          <t>标准日期</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>累计实际数</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>日期筛选器</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" s="13">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>类别2</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>排序</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>总类别</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="13">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>环节序号</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>全年预算数</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="13">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>产品分类</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>上月年月编码</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>累计实际数</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="13">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>月计划</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>月预算</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>标准日期</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
     </row>
     <row r="31" ht="22.05" customHeight="1" s="13">
       <c r="A31" s="14" t="inlineStr">
@@ -1260,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1338,17 +1286,17 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>630c17f</t>
+          <t>7148b64</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:29</t>
+          <t>2026-10-14 11:35:22</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -1363,7 +1311,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
+          <t>优化语义模型 M 代码与输出列</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -1372,13 +1320,13 @@
         </is>
       </c>
       <c r="I2" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2" s="12" t="n">
-        <v>69</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="13">
@@ -1387,17 +1335,17 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>1794160</t>
+          <t>f996ae9</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:24</t>
+          <t>2026-10-14 11:35:16</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1412,7 +1360,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>调整报告视觉对象布局与筛选</t>
+          <t>调整报告页面命名与日报日期筛选</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -1421,13 +1369,13 @@
         </is>
       </c>
       <c r="I3" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="13">
@@ -1436,17 +1384,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>9cbf408</t>
+          <t>630c17f</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:18</t>
+          <t>2026-10-14 10:06:29</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1461,7 +1409,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>修复语义模型分析报告发现的问题</t>
+          <t>更新语义模型分析报告：同步本轮修复</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1470,13 +1418,13 @@
         </is>
       </c>
       <c r="I4" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="13">
@@ -1485,17 +1433,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>07f180b</t>
+          <t>1794160</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 07:21:58</t>
+          <t>2026-10-14 10:06:24</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1510,7 +1458,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+          <t>调整报告视觉对象布局与筛选</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1519,13 +1467,13 @@
         </is>
       </c>
       <c r="I5" s="15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="13">
@@ -1534,17 +1482,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2d4f16f</t>
+          <t>9cbf408</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 07:01:02</t>
+          <t>2026-10-14 10:06:18</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1559,7 +1507,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
+          <t>修复语义模型分析报告发现的问题</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1568,13 +1516,13 @@
         </is>
       </c>
       <c r="I6" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>320</v>
+        <v>86</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="13">
@@ -1583,17 +1531,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>5ba71b7</t>
+          <t>07f180b</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 06:57:45</t>
+          <t>2026-10-14 07:21:58</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1608,7 +1556,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1617,13 +1565,13 @@
         </is>
       </c>
       <c r="I7" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="13">
@@ -1632,17 +1580,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>cea3882</t>
+          <t>2d4f16f</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 06:34:36</t>
+          <t>2026-10-14 07:01:02</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1657,7 +1605,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>优化语义模型自定义函数命名</t>
+          <t>新增 KFM日月报语义模型分析报告</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1666,13 +1614,13 @@
         </is>
       </c>
       <c r="I8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>17</v>
+        <v>320</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="13">
@@ -1681,17 +1629,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>9f32794</t>
+          <t>5ba71b7</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 06:22:46</t>
+          <t>2026-10-14 06:57:45</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1706,7 +1654,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -1715,13 +1663,13 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>695</v>
+        <v>10</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>697</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="13">
@@ -1730,17 +1678,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>07301c6</t>
+          <t>cea3882</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:57:45</t>
+          <t>2026-10-14 06:34:36</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -1755,7 +1703,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+          <t>优化语义模型自定义函数命名</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -1764,13 +1712,13 @@
         </is>
       </c>
       <c r="I10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="13">
@@ -1779,17 +1727,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>1485d55</t>
+          <t>9f32794</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:45:55</t>
+          <t>2026-10-14 06:22:46</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1804,7 +1752,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -1813,13 +1761,13 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>134</v>
+        <v>695</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>227</v>
+        <v>697</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="13">
@@ -1828,17 +1776,17 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>6b4084c</t>
+          <t>07301c6</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:31:50</t>
+          <t>2026-10-13 19:57:45</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1853,7 +1801,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1865,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="13">
@@ -1877,17 +1825,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>1485d55</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-13 19:45:55</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1902,7 +1850,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -1914,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>28</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="13">
@@ -1926,17 +1874,17 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>48112a2</t>
+          <t>6b4084c</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 18:55:27</t>
+          <t>2026-10-13 19:31:50</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1951,7 +1899,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1960,13 +1908,13 @@
         </is>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>5662</v>
+        <v>130</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>771</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="13">
@@ -1975,17 +1923,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>69bb2ba</t>
+          <t>2a59e2f</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 01:42:09</t>
+          <t>2026-10-13 19:15:18</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -2000,7 +1948,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
@@ -2009,13 +1957,13 @@
         </is>
       </c>
       <c r="I15" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="13">
@@ -2024,46 +1972,144 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="13">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="13">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>26750</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2078,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="13" min="1" max="1"/>
@@ -2101,12 +2147,51 @@
     <row r="3" ht="20" customHeight="1" s="13">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="149.5" customHeight="1" s="13">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列
+- 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
+- 精简月报/日报输出列，移除 类别/产线/指标类型/日期/指标名 等中间列
+- 映射表按 Sheet 名称取数，SharePoint 读取步骤由 6 步合并为 3 步
+- 末尾「删列+重排」合并为单步「保留最终列」
+- SAP 连接参数化统一到月报，补充步骤注释
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="134" customHeight="1" s="13">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选
+- 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
+- 日报视觉对象改用「日期筛选器」列，默认「最近日期」
+- 表格新增月计划L1/月比计划L1/年累计完成L1/年计划L1/年比计划L1 度量与「总类别」筛选
+- 调整表格行高、列宽与默认活动页
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="118.5" customHeight="1" s="13">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="8" ht="118.5" customHeight="1" s="13">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2116,15 +2201,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="13">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="9" ht="20" customHeight="1" s="13">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="118.5" customHeight="1" s="13">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="10" ht="118.5" customHeight="1" s="13">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2134,15 +2219,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="13">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="196" customHeight="1" s="13">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="12" ht="196" customHeight="1" s="13">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2157,15 +2242,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" s="13">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="118.5" customHeight="1" s="13">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="13">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2175,15 +2260,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="13">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="13">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="87.5" customHeight="1" s="13">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="16" ht="87.5" customHeight="1" s="13">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2191,15 +2276,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="13">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="103" customHeight="1" s="13">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="18" ht="103" customHeight="1" s="13">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2208,15 +2293,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" s="13">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="19" ht="20" customHeight="1" s="13">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="118.5" customHeight="1" s="13">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="20" ht="118.5" customHeight="1" s="13">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2226,15 +2311,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="13">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="13">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="87.5" customHeight="1" s="13">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="22" ht="87.5" customHeight="1" s="13">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2242,15 +2327,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1" s="13">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="23" ht="20" customHeight="1" s="13">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="87.5" customHeight="1" s="13">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="24" ht="87.5" customHeight="1" s="13">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2258,15 +2343,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" s="13">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="13">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="103" customHeight="1" s="13">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="26" ht="103" customHeight="1" s="13">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2275,15 +2360,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" s="13">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="27" ht="20" customHeight="1" s="13">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="134" customHeight="1" s="13">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="28" ht="134" customHeight="1" s="13">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2294,15 +2379,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="13">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="29" ht="20" customHeight="1" s="13">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="134" customHeight="1" s="13">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="30" ht="134" customHeight="1" s="13">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2313,15 +2398,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" s="13">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1" s="13">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="273.5" customHeight="1" s="13">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="32" ht="273.5" customHeight="1" s="13">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2340,30 +2425,30 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1" s="13">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="13">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="56.5" customHeight="1" s="13">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="34" ht="56.5" customHeight="1" s="13">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" s="13">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="35" ht="20" customHeight="1" s="13">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="506" customHeight="1" s="13">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="36" ht="506" customHeight="1" s="13">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2395,10 +2480,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
@@ -2415,6 +2496,10 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2622,13 +2707,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{167067B0-C95C-4D8B-B093-5C83C7776AB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0898B9-1117-48B3-ABAF-2E561BE15651}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C90D35-9711-472B-AD53-8939EF8495CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E5C0DCD-556E-43BF-B078-8CB43C7D7663}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2474163F-545A-44AE-B6FF-35C08FDAD181}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45074B6A-C436-4EA6-A8FD-FA6A16B4D270}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>7148b64</t>
+          <t>8c90e31</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+          <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:35:22</t>
+          <t>2026-10-14 12:08:57</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>优化语义模型 M 代码与输出列</t>
+          <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="I2" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="K2" s="12" t="n">
-        <v>375</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="13">
@@ -1335,17 +1335,17 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>f996ae9</t>
+          <t>7148b64</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:35:16</t>
+          <t>2026-10-14 11:35:22</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>调整报告页面命名与日报日期筛选</t>
+          <t>优化语义模型 M 代码与输出列</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="I3" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>57</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="13">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>630c17f</t>
+          <t>f996ae9</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:29</t>
+          <t>2026-10-14 11:35:16</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
+          <t>调整报告页面命名与日报日期筛选</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="13">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>1794160</t>
+          <t>630c17f</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:24</t>
+          <t>2026-10-14 10:06:29</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>调整报告视觉对象布局与筛选</t>
+          <t>更新语义模型分析报告：同步本轮修复</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="I5" s="15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="13">
@@ -1482,17 +1482,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>9cbf408</t>
+          <t>1794160</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 10:06:18</t>
+          <t>2026-10-14 10:06:24</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>修复语义模型分析报告发现的问题</t>
+          <t>调整报告视觉对象布局与筛选</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="I6" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="13">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>07f180b</t>
+          <t>9cbf408</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 07:21:58</t>
+          <t>2026-10-14 10:06:18</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+          <t>修复语义模型分析报告发现的问题</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="I7" s="15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="13">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2d4f16f</t>
+          <t>07f180b</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 07:01:02</t>
+          <t>2026-10-14 07:21:58</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1617,10 +1617,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="13">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>5ba71b7</t>
+          <t>2d4f16f</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 06:57:45</t>
+          <t>2026-10-14 07:01:02</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+          <t>新增 KFM日月报语义模型分析报告</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -1663,13 +1663,13 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>10</v>
+        <v>320</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="13">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>cea3882</t>
+          <t>5ba71b7</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 06:34:36</t>
+          <t>2026-10-14 06:57:45</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>优化语义模型自定义函数命名</t>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -1715,10 +1715,10 @@
         <v>2</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="13">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>9f32794</t>
+          <t>cea3882</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>2026-10-14 06:22:46</t>
+          <t>2026-10-14 06:34:36</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+          <t>优化语义模型自定义函数命名</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>695</v>
+        <v>17</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>697</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="13">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>07301c6</t>
+          <t>9f32794</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:57:45</t>
+          <t>2026-10-14 06:22:46</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>2</v>
+        <v>695</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>1</v>
+        <v>697</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="13">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>1485d55</t>
+          <t>07301c6</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:45:55</t>
+          <t>2026-10-13 19:57:45</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -1859,13 +1859,13 @@
         </is>
       </c>
       <c r="I13" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>227</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="13">
@@ -1874,17 +1874,17 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>6b4084c</t>
+          <t>1485d55</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 19:31:50</t>
+          <t>2026-10-13 19:45:55</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="I14" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>143</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="13">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2a59e2f</t>
+          <t>6b4084c</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 19:15:18</t>
+          <t>2026-10-13 19:31:50</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="I15" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="13">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>48112a2</t>
+          <t>2a59e2f</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 18:55:27</t>
+          <t>2026-10-13 19:15:18</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="I16" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>5662</v>
+        <v>21</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>771</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="13">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>69bb2ba</t>
+          <t>48112a2</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>2026-10-13 01:42:09</t>
+          <t>2026-10-13 18:55:27</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0</v>
+        <v>5662</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="13">
@@ -2070,46 +2070,95 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="13">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
           <t>248840e</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>2026-10-13 01:07:27</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I19" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J19" s="15" t="n">
         <v>26750</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K19" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2124,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="13" min="1" max="1"/>
@@ -2147,12 +2196,30 @@
     <row r="3" ht="20" customHeight="1" s="13">
       <c r="A3" s="10" t="inlineStr">
         <is>
+          <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="118.5" customHeight="1" s="13">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步 M 优化与列精简
+- 模型总览列数同步：月报 18 列、日报 15 列
+- 补充「日期筛选器」列与收列步骤，SAP 连接参数化说明
+- 移除已修复的映射表行索引问题，更新问题计数与改进清单
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="149.5" customHeight="1" s="13">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="6" ht="149.5" customHeight="1" s="13">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2164,15 +2231,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="13">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="134" customHeight="1" s="13">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="8" ht="134" customHeight="1" s="13">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2183,15 +2250,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="13">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="9" ht="20" customHeight="1" s="13">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="118.5" customHeight="1" s="13">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="10" ht="118.5" customHeight="1" s="13">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2201,15 +2268,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" s="13">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="118.5" customHeight="1" s="13">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="13">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2219,15 +2286,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="13">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="196" customHeight="1" s="13">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="14" ht="196" customHeight="1" s="13">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2242,15 +2309,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="13">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.5" customHeight="1" s="13">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="16" ht="118.5" customHeight="1" s="13">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2260,15 +2327,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" s="13">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="13">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="87.5" customHeight="1" s="13">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18" ht="87.5" customHeight="1" s="13">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2276,15 +2343,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="13">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="19" ht="20" customHeight="1" s="13">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="103" customHeight="1" s="13">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="20" ht="103" customHeight="1" s="13">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2293,15 +2360,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1" s="13">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="13">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="118.5" customHeight="1" s="13">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="22" ht="118.5" customHeight="1" s="13">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2311,15 +2378,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" s="13">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23" ht="20" customHeight="1" s="13">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="87.5" customHeight="1" s="13">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="24" ht="87.5" customHeight="1" s="13">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2327,15 +2394,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" s="13">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="13">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="87.5" customHeight="1" s="13">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="26" ht="87.5" customHeight="1" s="13">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2343,15 +2410,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="13">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="27" ht="20" customHeight="1" s="13">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="103" customHeight="1" s="13">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="28" ht="103" customHeight="1" s="13">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2360,15 +2427,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" s="13">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="29" ht="20" customHeight="1" s="13">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="134" customHeight="1" s="13">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="30" ht="134" customHeight="1" s="13">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2379,15 +2446,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1" s="13">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1" s="13">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="134" customHeight="1" s="13">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="32" ht="134" customHeight="1" s="13">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2398,15 +2465,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" s="13">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="13">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="273.5" customHeight="1" s="13">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34" ht="273.5" customHeight="1" s="13">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2425,30 +2492,30 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1" s="13">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="35" ht="20" customHeight="1" s="13">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="56.5" customHeight="1" s="13">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="36" ht="56.5" customHeight="1" s="13">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1" s="13">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="37" ht="20" customHeight="1" s="13">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="506" customHeight="1" s="13">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="38" ht="506" customHeight="1" s="13">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2480,8 +2547,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39"/>
     <row r="40"/>
     <row r="41"/>
@@ -2500,6 +2565,8 @@
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2707,13 +2774,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0898B9-1117-48B3-ABAF-2E561BE15651}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBAFBC9B-9CC5-46A7-A885-B49738926A2B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E5C0DCD-556E-43BF-B078-8CB43C7D7663}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD84E6FE-D944-487F-83B9-5EFDAC61C0A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45074B6A-C436-4EA6-A8FD-FA6A16B4D270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD3A6EA-FE77-4820-A1CA-CE062FA69160}"/>
 </file>
--- a/项目版本信息.xlsx
+++ b/项目版本信息.xlsx
@@ -695,7 +695,7 @@
     <row r="1" ht="32" customHeight="1" s="13">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>L3报表-KFM日月报 项目概述</t>
+          <t>L3报表 项目概述</t>
         </is>
       </c>
       <c r="B1" s="24" t="n"/>
@@ -707,14 +707,14 @@
     <row r="2" ht="31.05" customHeight="1" s="13">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>L3报表-KFM日月报：KFM选冶厂月度/日报生产指标完成情况，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-14</t>
+          <t>L3报表：KFM选冶厂月度/日报生产指标完成情况，Power BI 项目格式（PBIP）。含报告（PBIR）与语义模型（TMDL）两部分，语言文化 zh-CN。最后更新：2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" s="13">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>一、报告层（L3报表-KFM日月报.Report）</t>
+          <t>一、报告层（L3报表.Report）</t>
         </is>
       </c>
     </row>
@@ -744,13 +744,13 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>KFM日报</t>
+          <t>日报</t>
         </is>
       </c>
       <c r="B6" s="25" t="n"/>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>日报落地页（5 个视觉对象）</t>
+          <t>日报页，视图模式下隐藏（5 个视觉对象）</t>
         </is>
       </c>
       <c r="D6" s="26" t="n"/>
@@ -776,13 +776,13 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>KFM月报</t>
+          <t>月报</t>
         </is>
       </c>
       <c r="B8" s="25" t="n"/>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>原始月报页（7 个视觉对象）</t>
+          <t>月报落地页（7 个视觉对象）</t>
         </is>
       </c>
       <c r="D8" s="26" t="n"/>
@@ -820,7 +820,7 @@
     <row r="11" ht="22.05" customHeight="1" s="13">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>二、语义模型（L3报表-KFM日月报.SemanticModel）</t>
+          <t>二、语义模型（L3报表.SemanticModel）</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
     <row r="13" ht="20" customHeight="1" s="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>事实表 KFM选冶厂月报（18 列）</t>
+          <t>事实表 KFM选冶厂月报（19 列）</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,11 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" s="13">
-      <c r="A20" s="3" t="n"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>指标类别</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1" s="13">
       <c r="A21" s="14" t="inlineStr">
@@ -1208,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -1286,879 +1290,928 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
+          <t>d6b1785</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>d6b1785b86f19f2db61866bfc840abcac3e1f2cf</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05:13</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="13">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
           <t>8c90e31</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>8c90e3154248a749ec3ef3bc61d68576b709d2f7</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>2026-10-14 12:08:57</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J3" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K3" s="12" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="13">
-      <c r="A3" s="15" t="n">
+    <row r="4" ht="30" customHeight="1" s="13">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>7148b64</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:22</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>优化语义模型 M 代码与输出列</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="13">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>f996ae9</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:35:16</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>调整报告页面命名与日报日期筛选</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="13">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>630c17f</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:29</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>更新语义模型分析报告：同步本轮修复</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="13">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>1794160</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:24</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>调整报告视觉对象布局与筛选</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="13">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>9cbf408</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:06:18</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>修复语义模型分析报告发现的问题</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>86</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="13">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>07f180b</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:21:58</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="13">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>2d4f16f</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:01:02</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>新增 KFM日月报语义模型分析报告</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>320</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="13">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>5ba71b7</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:57:45</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>7148b64</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>7148b64ddd4ee32a7c06e2f912d939dc2ba4e1b5</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:22</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="J11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="13">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>cea3882</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:34:36</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>优化语义模型 M 代码与输出列</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>优化语义模型自定义函数命名</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I3" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="13">
-      <c r="A4" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>f996ae9</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>f996ae982e67b13a495117c8a9b34531f4eded82</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:35:16</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="I12" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>9f32794</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:22:46</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>调整报告页面命名与日报日期筛选</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="13">
-      <c r="A5" s="15" t="n">
+      <c r="I13" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>695</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="13">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>07301c6</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:57:45</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="13">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>1485d55</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:45:55</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>630c17f</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>630c17fceaf47b46c21633e044fda78155ac0443</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:29</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="J15" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="13">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>6b4084c</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:31:50</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>更新语义模型分析报告：同步本轮修复</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="15" t="n">
+      <c r="J16" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="13">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2a59e2f</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 19:15:18</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="13">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>48112a2</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:55:27</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Jevon Zhu</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>jevonzhu2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="K5" s="15" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="13">
-      <c r="A6" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>1794160</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>179416093e3aff5472f3a2f4719d2270cff850d1</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:24</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="J18" s="15" t="n">
+        <v>5662</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="13">
+      <c r="A19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>69bb2ba</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:42:09</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>调整报告视觉对象布局与筛选</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="13">
-      <c r="A7" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>9cbf408</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>9cbf408d9186e1be6583b91b3e445288720dab30</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14 10:06:18</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="I19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="13">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>248840e</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13 01:07:27</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Jevon Zhu</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>jevonzhu2008@gmail.com</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>修复语义模型分析报告发现的问题</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="13">
-      <c r="A8" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>07f180b</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>07f180b9740c0c72f4ff4cb637acce0c8b718efc</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:21:58</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>修正日报度量值：清理标题围栏并调整年累计完成字段</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="13">
-      <c r="A9" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>2d4f16f</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>2d4f16fda737382909dd93ca2b175b6618fcbb57</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14 07:01:02</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>新增 KFM日月报语义模型分析报告</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>320</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="13">
-      <c r="A10" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>5ba71b7</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>5ba71b7bdd8c9fa3140791e2c325425796229e13</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:57:45</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>修正 DAX/M 代码注释，准确反映实际逻辑</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="13">
-      <c r="A11" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>cea3882</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>cea3882903b1e0ebd284ee0a2acadb18380ddd7f</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:34:36</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>优化语义模型自定义函数命名</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="13">
-      <c r="A12" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>9f32794</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>9f32794cc45bd00e695f720d0e38ca7eda0ee97d</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:22:46</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>695</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="13">
-      <c r="A13" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>07301c6</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>07301c63639499dc1642f9abe29a9baee1e0c3cf</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:57:45</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>修复 KFM选冶厂月报 TMDL 缩进错误</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="13">
-      <c r="A14" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>1485d55</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>1485d55c4d5b2c241eb05e9040a3897476085331</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:45:55</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>优化全部 M 查询：步骤名语义化与步骤合并</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="13">
-      <c r="A15" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>6b4084c</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>6b4084c9a3fb078c53fcbdd2549a2adc1fc7d100</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:31:50</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：命名注释与步骤精简</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="13">
-      <c r="A16" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>2a59e2f</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2a59e2f68de3a82d02c6493c75d4a170ce013fae</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-13 19:15:18</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>优化L1-KFM日报 M 查询：内联两个中间表</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="13">
-      <c r="A17" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>48112a2</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>48112a2bfe1b2809ef94fe779a2e7a6c65d60bb2</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:55:27</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>5662</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="13">
-      <c r="A18" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>69bb2ba</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>69bb2ba9dc7aa839a00235f2ef0ed1b691d7384e</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:42:09</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="13">
-      <c r="A19" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>248840e</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>248840e9d232eacba69832ed5401065fb3ce1cab</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13 01:07:27</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>Jevon Zhu</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>jevonzhu2008@gmail.com</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="I19" s="15" t="n">
+      <c r="I20" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J20" s="15" t="n">
         <v>26750</v>
       </c>
-      <c r="K19" s="15" t="n">
+      <c r="K20" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2173,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="112" customWidth="1" style="13" min="1" max="1"/>
@@ -2196,12 +2249,31 @@
     <row r="3" ht="20" customHeight="1" s="13">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+          <t>提交 d6b1785 ｜ 2026-10-14 14:05:13 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="118.5" customHeight="1" s="13">
       <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>重命名报表项目：L3报表-KFM日月报 → L3报表
+- 项目、报告、语义模型整体重命名为 L3报表（目录、.pbip、.platform、definition.pbir 同步更新）
+- 页面更名：KFM月报 → 月报、KFM日报 → 日报
+- 日报页设为视图模式隐藏，落地页与活动页改为月报
+- 语义模型 KFM选冶厂月报 新增「指标类别」列（18→19 列），收列步骤合并并调整最终列顺序
+Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="13">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>提交 8c90e31 ｜ 2026-10-14 12:08:57 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118.5" customHeight="1" s="13">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步 M 优化与列精简
 - 模型总览列数同步：月报 18 列、日报 15 列
@@ -2211,15 +2283,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="13">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="13">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>提交 7148b64 ｜ 2026-10-14 11:35:22 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="149.5" customHeight="1" s="13">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="8" ht="149.5" customHeight="1" s="13">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>优化语义模型 M 代码与输出列
 - 日报新增「日期筛选器」列（按「原矿处理量」最大标准日期标记「最近日期」）
@@ -2231,15 +2303,15 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="13">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="9" ht="20" customHeight="1" s="13">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>提交 f996ae9 ｜ 2026-10-14 11:35:16 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="134" customHeight="1" s="13">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="10" ht="134" customHeight="1" s="13">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>调整报告页面命名与日报日期筛选
 - 页面更名：KFM选冶厂月报UI Enhance → KFM月报UIE、KFM选冶厂月报 → KFM月报
@@ -2250,15 +2322,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" s="13">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="11" ht="20" customHeight="1" s="13">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>提交 630c17f ｜ 2026-10-14 10:06:29 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="118.5" customHeight="1" s="13">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="12" ht="118.5" customHeight="1" s="13">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>更新语义模型分析报告：同步本轮修复
 - 同步年累计完成L1 新口径与新增参数、中间表变化
@@ -2268,15 +2340,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="13">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="13" ht="20" customHeight="1" s="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>提交 1794160 ｜ 2026-10-14 10:06:24 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="118.5" customHeight="1" s="13">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="14" ht="118.5" customHeight="1" s="13">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>调整报告视觉对象布局与筛选
 - 按钮/书签视觉对象位置与尺寸微调
@@ -2286,15 +2358,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="13">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>提交 9cbf408 ｜ 2026-10-14 10:06:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="196" customHeight="1" s="13">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="16" ht="196" customHeight="1" s="13">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>修复语义模型分析报告发现的问题
 - 年累计完成L1 口径修正：累计预测数 → 累计实际数（新增列，经上月编码关联月报），消除重复计算
@@ -2309,15 +2381,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" s="13">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="13">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>提交 07f180b ｜ 2026-10-14 07:21:58 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="118.5" customHeight="1" s="13">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18" ht="118.5" customHeight="1" s="13">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>修正日报度量值：清理标题围栏并调整年累计完成字段
 - 标题-日报：移除多余的三反引号围栏标记，修复 TMDL 语法解析
@@ -2327,15 +2399,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" s="13">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="19" ht="20" customHeight="1" s="13">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>提交 2d4f16f ｜ 2026-10-14 07:01:02 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="87.5" customHeight="1" s="13">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="20" ht="87.5" customHeight="1" s="13">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>新增 KFM日月报语义模型分析报告
 HTML 分析报告，涵盖模型总览、M 转换逻辑、DAX 计算逻辑与分级问题清单。
@@ -2343,15 +2415,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1" s="13">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="13">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>提交 5ba71b7 ｜ 2026-10-14 06:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="103" customHeight="1" s="13">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="22" ht="103" customHeight="1" s="13">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>修正 DAX/M 代码注释，准确反映实际逻辑
 - functions.tmdl：修正 FormatAmount/FormatRatio 的格式注释（两位小数/差额/百分比），SameMonthPriorYear 顶部注释去掉「年累计实际数」限定
@@ -2360,15 +2432,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" s="13">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="23" ht="20" customHeight="1" s="13">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>提交 cea3882 ｜ 2026-10-14 06:34:36 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="118.5" customHeight="1" s="13">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="24" ht="118.5" customHeight="1" s="13">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>优化语义模型自定义函数命名
 - FormatKFM → FormatAmount（数量格式）
@@ -2378,15 +2450,15 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" s="13">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="13">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>提交 9f32794 ｜ 2026-10-14 06:22:46 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="87.5" customHeight="1" s="13">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="26" ht="87.5" customHeight="1" s="13">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>重命名报表项目：KFM选冶厂月报 → L3报表-KFM日月报
 删除旧项目文件，改用新项目名称。
@@ -2394,15 +2466,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="13">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="27" ht="20" customHeight="1" s="13">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>提交 07301c6 ｜ 2026-10-13 19:57:45 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="87.5" customHeight="1" s="13">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="28" ht="87.5" customHeight="1" s="13">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>修复 KFM选冶厂月报 TMDL 缩进错误
 将 source 的 M 代码改为三反引号形式，修复 let 顶格导致的 TMDL 缩进解析错误。
@@ -2410,15 +2482,15 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" s="13">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="29" ht="20" customHeight="1" s="13">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>提交 1485d55 ｜ 2026-10-13 19:45:55 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="103" customHeight="1" s="13">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="30" ht="103" customHeight="1" s="13">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>优化全部 M 查询：步骤名语义化与步骤合并
 - KFM选冶厂月报：Cube.Transform 直接输出最终列名，删除「重命名列」「新增指标项列」步骤；去掉未使用的产品、矿坑、指标编码维度；合并类别2分组逻辑与最近月份计算；步骤名统一中文
@@ -2427,15 +2499,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1" s="13">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1" s="13">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>提交 6b4084c ｜ 2026-10-13 19:31:50 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="134" customHeight="1" s="13">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="32" ht="134" customHeight="1" s="13">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：命名注释与步骤精简
 - Cube.Transform 直接输出最终列名，删除冗余的「重命名的列」步骤
@@ -2446,15 +2518,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" s="13">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="13">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>提交 2a59e2f ｜ 2026-10-13 19:15:18 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="134" customHeight="1" s="13">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34" ht="134" customHeight="1" s="13">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>优化L1-KFM日报 M 查询：内联两个中间表
 - 将 全年预算表、月累计预测表 两个中间表 expression 内联进 L1-KFM日报 的 M 查询，消除跨查询依赖
@@ -2465,15 +2537,15 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1" s="13">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="35" ht="20" customHeight="1" s="13">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>提交 48112a2 ｜ 2026-10-13 18:55:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="273.5" customHeight="1" s="13">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="36" ht="273.5" customHeight="1" s="13">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>升级语义模型兼容级别1702，新增日报模型与DAX函数(UDF)
 语义模型
@@ -2492,30 +2564,30 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1" s="13">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="37" ht="20" customHeight="1" s="13">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>提交 69bb2ba ｜ 2026-10-13 01:42:09 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="56.5" customHeight="1" s="13">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="38" ht="56.5" customHeight="1" s="13">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>新增项目版本信息 Excel 文档（含项目概述、Git版本历史、提交备注）
 Co-Authored-By: Claude Fable 5.1 &lt;noreply@anthropic.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1" s="13">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="39" ht="20" customHeight="1" s="13">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>提交 248840e ｜ 2026-10-13 01:07:27 ｜ Jevon Zhu &lt;jevonzhu2008@gmail.com&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="506" customHeight="1" s="13">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="40" ht="506" customHeight="1" s="13">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>初始化存档：KFM选冶厂月报 Power BI 项目（PBIP）
 项目概述
@@ -2547,26 +2619,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2774,13 +2826,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBAFBC9B-9CC5-46A7-A885-B49738926A2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F2BA6DF-5710-4599-9464-8B5704A88B28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD84E6FE-D944-487F-83B9-5EFDAC61C0A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990E41BB-116C-4E41-A332-6977811113F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD3A6EA-FE77-4820-A1CA-CE062FA69160}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2D89E71-8500-4581-89CA-53CE8B548322}"/>
 </file>